--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487675_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487675_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3671</v>
+        <v>6.0611</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4188</v>
+        <v>4.8402</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9483</v>
+        <v>1.2208</v>
       </c>
       <c r="G2" t="n">
         <v>2.0006</v>
@@ -610,13 +610,13 @@
         <v>3.1045</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3275</v>
+        <v>0.3665</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3982</v>
+        <v>0.0232</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0707</v>
+        <v>0.3432</v>
       </c>
       <c r="V2" t="n">
         <v>4.4701</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FRANCES PASCUAL</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2859</v>
+        <v>4.7589</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0298</v>
+        <v>4.6848</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2561</v>
+        <v>0.0741</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7333</v>
+        <v>1.1123</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3907</v>
+        <v>0.7291</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3426</v>
+        <v>0.3832</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3798</v>
+        <v>2.0771</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2986</v>
+        <v>1.4047</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.6724</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6466</v>
+        <v>-0.9648</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9079</v>
+        <v>-0.6756</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2614</v>
+        <v>-0.2892</v>
       </c>
       <c r="P3" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9403</v>
+        <v>-2.1344</v>
       </c>
       <c r="R3" t="n">
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6989</v>
+        <v>-0.0249</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5904</v>
+        <v>-0.1534</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1086</v>
+        <v>0.1285</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6597</v>
+        <v>3.6716</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>4.8955</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6597</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0616</v>
+        <v>4.5128</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1238</v>
+        <v>6.2992</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0621</v>
+        <v>-1.7864</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1123</v>
+        <v>3.2876</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7291</v>
+        <v>3.5089</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3832</v>
+        <v>-0.2213</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0771</v>
+        <v>4.5137</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4047</v>
+        <v>4.5849</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6724</v>
+        <v>-0.0711</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9648</v>
+        <v>-1.2262</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6756</v>
+        <v>-1.076</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2892</v>
+        <v>-0.1502</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.5523</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1344</v>
+        <v>2.5224</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7223000000000001</v>
+        <v>0.2849</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7145</v>
+        <v>0.0258</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0078</v>
+        <v>0.2591</v>
       </c>
       <c r="V4" t="n">
-        <v>3.6716</v>
+        <v>-0.6119</v>
       </c>
       <c r="W4" t="n">
-        <v>4.8955</v>
+        <v>2.7298</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2239</v>
+        <v>-3.3418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>J. FRANCES PASCUAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0352</v>
+        <v>3.5546</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2531</v>
+        <v>1.1895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7821</v>
+        <v>2.3651</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9265</v>
+        <v>1.7333</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2051</v>
+        <v>1.3907</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1317</v>
+        <v>0.3426</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5898</v>
+        <v>2.3798</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1689</v>
+        <v>2.2986</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4209</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6633</v>
+        <v>-0.6466</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.374</v>
+        <v>-0.9079</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2892</v>
+        <v>0.2614</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9403</v>
+        <v>0.194</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9403</v>
+        <v>2.1344</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0623</v>
+        <v>0.9676</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6633</v>
+        <v>0.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3991</v>
+        <v>0.2176</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.894</v>
+        <v>0.6597</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.894</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7824</v>
+        <v>3.3851</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8392</v>
+        <v>1.6601</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9431</v>
+        <v>1.7251</v>
       </c>
       <c r="G6" t="n">
         <v>3.6619</v>
@@ -922,13 +922,13 @@
         <v>1.7463</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5085</v>
+        <v>0.1113</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1077</v>
+        <v>-0.2869</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6162</v>
+        <v>0.3982</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7544</v>
+        <v>3.3039</v>
       </c>
       <c r="E7" t="n">
-        <v>5.3772</v>
+        <v>2.4127</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6229</v>
+        <v>0.8911</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2876</v>
+        <v>0.9265</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5089</v>
+        <v>-0.2051</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2213</v>
+        <v>1.1317</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5137</v>
+        <v>1.5898</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5849</v>
+        <v>0.1689</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0711</v>
+        <v>1.4209</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2262</v>
+        <v>-0.6633</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.076</v>
+        <v>-0.374</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1502</v>
+        <v>-0.2892</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5224</v>
+        <v>1.9403</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4735</v>
+        <v>1.331</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8962</v>
+        <v>0.8229</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4226</v>
+        <v>0.5081</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6119</v>
+        <v>-0.894</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7298</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.3418</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6881</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>-0.04</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6481</v>
+        <v>-0.5936</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3969</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2912</v>
+        <v>-0.2366</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2306</v>
+        <v>-0.1761</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. GACIC</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5759</v>
+        <v>-2.6125</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.4108</v>
+        <v>-5.0196</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8348</v>
+        <v>2.4071</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0171</v>
+        <v>-3.8283</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1673</v>
+        <v>-1.4904</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1502</v>
+        <v>-2.3379</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2152</v>
+        <v>-3.7539</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.243</v>
+        <v>-1.1658</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0279</v>
+        <v>-2.5881</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1981</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.3246</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1223</v>
+        <v>0.2502</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.2687</v>
+        <v>1.5523</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.015</v>
+        <v>-1.1642</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7463</v>
+        <v>2.7164</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7203000000000001</v>
+        <v>-0.3365</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1806</v>
+        <v>-0.1015</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9009</v>
+        <v>-0.2349</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9896</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>S. GACIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5795</v>
+        <v>-3.3125</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.7413</v>
+        <v>-6.6295</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1618</v>
+        <v>3.317</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.8283</v>
+        <v>-0.0171</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4904</v>
+        <v>-0.1673</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3379</v>
+        <v>0.1502</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.7539</v>
+        <v>-0.2152</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1658</v>
+        <v>-0.243</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.5881</v>
+        <v>0.0279</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07439999999999999</v>
+        <v>0.1981</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3246</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2502</v>
+        <v>0.1223</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5523</v>
+        <v>-4.2687</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1642</v>
+        <v>-6.015</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7164</v>
+        <v>1.7463</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3035</v>
+        <v>-0.0162</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8233</v>
+        <v>-0.3993</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4802</v>
+        <v>0.3831</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.9896</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.9896</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.639</v>
+        <v>-5.3054</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.285</v>
+        <v>-2.9241</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3541</v>
+        <v>-2.3813</v>
       </c>
       <c r="G11" t="n">
         <v>-1.721</v>
@@ -1312,13 +1312,13 @@
         <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7225</v>
+        <v>-0.3889</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6057</v>
+        <v>-0.2448</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1168</v>
+        <v>-0.1441</v>
       </c>
       <c r="V11" t="n">
         <v>-3.3895</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.8041</v>
+        <v>13.7124</v>
       </c>
       <c r="E12" t="n">
-        <v>5.564800000000002</v>
+        <v>6.473300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>7.239</v>
+        <v>7.239000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>6.758900000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7291</v>
+        <v>4.729100000000001</v>
       </c>
       <c r="I12" t="n">
         <v>2.03</v>
@@ -1378,7 +1378,7 @@
         <v>-5.2481</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8344999999999999</v>
+        <v>-0.8345</v>
       </c>
       <c r="P12" t="n">
         <v>5.551115123125783e-17</v>
@@ -1390,16 +1390,16 @@
         <v>19.4032</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1495</v>
+        <v>2.0582</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5331000000000001</v>
+        <v>0.3754000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>1.6827</v>
       </c>
       <c r="V12" t="n">
-        <v>4.895600000000002</v>
+        <v>4.8956</v>
       </c>
       <c r="W12" t="n">
         <v>12.6596</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1805</v>
+        <v>4.7989</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5294</v>
+        <v>2.9298</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6511</v>
+        <v>1.8691</v>
       </c>
       <c r="G13" t="n">
         <v>1.8034</v>
@@ -1468,13 +1468,13 @@
         <v>2.3284</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6183999999999999</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5933</v>
+        <v>-0.1929</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0251</v>
+        <v>0.1929</v>
       </c>
       <c r="V13" t="n">
         <v>2.6074</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.93</v>
+        <v>1.2749</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2741</v>
+        <v>-0.3265</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6559</v>
+        <v>1.6014</v>
       </c>
       <c r="G14" t="n">
         <v>0.7292999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>1.5523</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6187</v>
+        <v>-0.0364</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7896</v>
+        <v>0.189</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1709</v>
+        <v>-0.2254</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1074</v>
+        <v>-0.2958</v>
       </c>
       <c r="E15" t="n">
-        <v>0.476</v>
+        <v>0.0756</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3685</v>
+        <v>-0.3713</v>
       </c>
       <c r="G15" t="n">
         <v>-1.14</v>
@@ -1624,13 +1624,13 @@
         <v>1.7463</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9892</v>
+        <v>0.586</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3174</v>
+        <v>-0.083</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6718</v>
+        <v>0.669</v>
       </c>
       <c r="V15" t="n">
         <v>0.4522</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>M. ESTAPE ROIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4844</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7544999999999999</v>
+        <v>-1.2259</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2701</v>
+        <v>0.68</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.5934</v>
+        <v>2.5123</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.9412</v>
+        <v>0.3485</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6523</v>
+        <v>2.1638</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.2231</v>
+        <v>2.6537</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.6775</v>
+        <v>0.7456</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5455</v>
+        <v>1.908</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3704</v>
+        <v>-0.1413</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2637</v>
+        <v>-0.3971</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1067</v>
+        <v>0.2558</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>-3.8806</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9105</v>
+        <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0747</v>
+        <v>0.106</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3492</v>
+        <v>0.0011</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7255</v>
+        <v>0.1049</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0642</v>
+        <v>-1.2239</v>
       </c>
       <c r="W16" t="n">
-        <v>3.0597</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.9955</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ESTAPE ROIZ</t>
+          <t>T. VERDERA BENASSAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9246</v>
+        <v>-1.1341</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2259</v>
+        <v>-0.9182</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3012</v>
+        <v>-0.2159</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5123</v>
+        <v>0.1862</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3485</v>
+        <v>-1.3454</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1638</v>
+        <v>1.5315</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6537</v>
+        <v>0.4204</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7456</v>
+        <v>-1.5283</v>
       </c>
       <c r="L17" t="n">
-        <v>1.908</v>
+        <v>1.9486</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1413</v>
+        <v>-0.2342</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3971</v>
+        <v>0.1829</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2558</v>
+        <v>-0.4171</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9403</v>
+        <v>1.5523</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9403</v>
+        <v>2.5224</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2728</v>
+        <v>-0.1054</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0011</v>
+        <v>-0.3685</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2739</v>
+        <v>0.263</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2239</v>
+        <v>-2.7671</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2239</v>
+        <v>-2.7671</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. VERDERA BENASSAR</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.98</v>
+        <v>-1.7157</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5188</v>
+        <v>-1.9557</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4612</v>
+        <v>0.24</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1862</v>
+        <v>-4.5934</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3454</v>
+        <v>-2.9412</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5315</v>
+        <v>-1.6523</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4204</v>
+        <v>-3.2231</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5283</v>
+        <v>-2.6775</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9486</v>
+        <v>-0.5455</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2342</v>
+        <v>-1.3704</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1829</v>
+        <v>-0.2637</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4171</v>
+        <v>-1.1067</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5523</v>
+        <v>0.9702</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5224</v>
+        <v>2.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9513</v>
+        <v>0.8434</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9691</v>
+        <v>0.148</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0177</v>
+        <v>0.6954</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.7671</v>
+        <v>1.0642</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.0597</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7671</v>
+        <v>-1.9955</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1233</v>
+        <v>-1.7557</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3138</v>
+        <v>-1.9134</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1905</v>
+        <v>0.1577</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3232</v>
@@ -1936,13 +1936,13 @@
         <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7225</v>
+        <v>-0.355</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7268</v>
+        <v>-0.3264</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0043</v>
+        <v>-0.0286</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6597</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. FATA ALCARAZ</t>
+          <t>L. SCHIEBELHUT LUIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3435</v>
+        <v>-1.9339</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4653</v>
+        <v>1.4031</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8782</v>
+        <v>-3.337</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.67</v>
+        <v>-0.5343</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2348</v>
+        <v>-3.1909</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9048</v>
+        <v>2.6566</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2354</v>
+        <v>1.4317</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3913</v>
+        <v>-1.1081</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6267</v>
+        <v>2.5398</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4346</v>
+        <v>-1.966</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1565</v>
+        <v>-2.0828</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2781</v>
+        <v>0.1168</v>
       </c>
       <c r="P20" t="n">
-        <v>0.194</v>
+        <v>1.5523</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.194</v>
+        <v>1.5523</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5213</v>
+        <v>0.2675</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2299</v>
+        <v>-0.0286</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2914</v>
+        <v>0.2961</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3463</v>
+        <v>-3.2194</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3463</v>
+        <v>-3.2194</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. SCHIEBELHUT LUIS</t>
+          <t>G. FATA ALCARAZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4311</v>
+        <v>-1.9465</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2029</v>
+        <v>-0.3652</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.634</v>
+        <v>-1.5812</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5343</v>
+        <v>-0.67</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.1909</v>
+        <v>0.2348</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6566</v>
+        <v>-0.9048</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4317</v>
+        <v>-0.2354</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1081</v>
+        <v>0.3913</v>
       </c>
       <c r="L21" t="n">
-        <v>2.5398</v>
+        <v>-0.6267</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.966</v>
+        <v>-0.4346</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0828</v>
+        <v>-0.1565</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1168</v>
+        <v>-0.2781</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5523</v>
+        <v>0.194</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5523</v>
+        <v>0.194</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2297</v>
+        <v>-0.1242</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2288</v>
+        <v>-0.1298</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0009</v>
+        <v>0.0056</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.2194</v>
+        <v>-1.3463</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.2194</v>
+        <v>-1.3463</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1257</v>
+        <v>-2.7376</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7359</v>
+        <v>-1.5357</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3899</v>
+        <v>-1.2019</v>
       </c>
       <c r="G22" t="n">
         <v>-4.2157</v>
@@ -2170,13 +2170,13 @@
         <v>0.7761</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1638</v>
+        <v>-0.7756</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6662</v>
+        <v>-0.466</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4975</v>
+        <v>-0.3095</v>
       </c>
       <c r="V22" t="n">
         <v>2.4477</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6091</v>
+        <v>-5.478</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7072</v>
+        <v>-3.4069</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9019</v>
+        <v>-2.071</v>
       </c>
       <c r="G23" t="n">
         <v>0.4866</v>
@@ -2248,13 +2248,13 @@
         <v>2.3284</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3524</v>
+        <v>-0.2212</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7257</v>
+        <v>-0.4254</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3733</v>
+        <v>0.2042</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2507</v>
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.8038</v>
+        <v>-11.4694</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.239</v>
+        <v>-7.239000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.5649</v>
+        <v>-4.2301</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.7588</v>
+        <v>-6.758799999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.7291</v>
+        <v>-4.729100000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-2.0301</v>
       </c>
       <c r="J24" t="n">
-        <v>6.082600000000001</v>
+        <v>6.082599999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>5.248199999999999</v>
+        <v>5.248200000000001</v>
       </c>
       <c r="L24" t="n">
         <v>0.8344000000000004</v>
@@ -2323,19 +2323,19 @@
         <v>-19.4033</v>
       </c>
       <c r="R24" t="n">
-        <v>19.4033</v>
+        <v>19.40329999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1496</v>
+        <v>0.1851</v>
       </c>
       <c r="T24" t="n">
         <v>-1.6825</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5329000000000002</v>
+        <v>1.8676</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.895599999999999</v>
+        <v>-4.8956</v>
       </c>
       <c r="W24" t="n">
         <v>7.7641</v>
